--- a/data/B24_department_schedules_finals/Çevre Mühendisliği.xlsx
+++ b/data/B24_department_schedules_finals/Çevre Mühendisliği.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e402f802124af4b/Masaüstü/Projects/Campus-Scheduling/data/department_schedules_finals/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e402f802124af4b/Masaüstü/Projects/Campus-Scheduling/data/B24_department_schedules_finals/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{EAF33FDF-CB85-45B9-813E-3BECDF2DB8E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{935BB47C-7E2C-42CE-8E6F-20D7937AAC38}"/>
+  <xr:revisionPtr revIDLastSave="57" documentId="13_ncr:1_{EAF33FDF-CB85-45B9-813E-3BECDF2DB8E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91AA2DD8-2217-4BB3-9D82-C8ED5B6B9937}"/>
   <bookViews>
-    <workbookView xWindow="-17640" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20760" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="65">
   <si>
     <t>Year:</t>
   </si>
@@ -212,6 +212,9 @@
   </si>
   <si>
     <t>YLAB 1</t>
+  </si>
+  <si>
+    <t>timeslots</t>
   </si>
 </sst>
 </file>
@@ -292,7 +295,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -309,11 +312,18 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="11">
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -392,15 +402,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E703AF2A-1E55-474A-BE3F-96016289569F}" name="Table1" displayName="Table1" ref="A1:F27" totalsRowShown="0" headerRowDxfId="9" dataDxfId="7" headerRowBorderDxfId="8" tableBorderDxfId="6">
-  <autoFilter ref="A1:F27" xr:uid="{E703AF2A-1E55-474A-BE3F-96016289569F}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{3ECC80F5-2B5A-409B-A2FF-F6F263A9CF08}" name="Year:" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{4CC3476D-C67B-428F-9A5C-322F2371A48D}" name="Course ID" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{9E31BA35-1BAC-4638-9AAB-E2F5DECBFAA7}" name="Date" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{2346AB05-A96B-4701-BDE3-56F34456BD03}" name="Rooms" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{C1888443-E59A-4029-842A-83485EAAED9D}" name="Course Name" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{43FBA85C-D7FD-4436-A5BA-F00F9D7917BC}" name="Rooms Used" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E703AF2A-1E55-474A-BE3F-96016289569F}" name="Table1" displayName="Table1" ref="A1:G27" totalsRowShown="0" headerRowDxfId="10" dataDxfId="8" headerRowBorderDxfId="9" tableBorderDxfId="7">
+  <autoFilter ref="A1:G27" xr:uid="{E703AF2A-1E55-474A-BE3F-96016289569F}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{3ECC80F5-2B5A-409B-A2FF-F6F263A9CF08}" name="Year:" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{4CC3476D-C67B-428F-9A5C-322F2371A48D}" name="Course ID" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{9E31BA35-1BAC-4638-9AAB-E2F5DECBFAA7}" name="Date" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{2346AB05-A96B-4701-BDE3-56F34456BD03}" name="Rooms" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{C1888443-E59A-4029-842A-83485EAAED9D}" name="Course Name" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{43FBA85C-D7FD-4436-A5BA-F00F9D7917BC}" name="Rooms Used" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{3CDF0D24-D53A-4BAB-8B96-ECB1A5CCF3F7}" name="timeslots" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -693,7 +704,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="10.9296875" customWidth="1"/>
@@ -701,7 +712,7 @@
     <col min="6" max="6" width="50.46484375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -720,8 +731,11 @@
       <c r="F1" s="1" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G1" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -740,8 +754,12 @@
       <c r="F2" s="2" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G2" s="7">
+        <v>2</v>
+      </c>
+      <c r="I2" s="6"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -760,8 +778,12 @@
       <c r="F3" s="2" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G3" s="7">
+        <v>7</v>
+      </c>
+      <c r="I3" s="6"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -780,8 +802,12 @@
       <c r="F4" s="2" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G4" s="7">
+        <v>7</v>
+      </c>
+      <c r="I4" s="6"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" s="2">
         <v>1</v>
       </c>
@@ -800,8 +826,12 @@
       <c r="F5" s="2" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G5" s="7">
+        <v>8</v>
+      </c>
+      <c r="I5" s="6"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" s="2">
         <v>1</v>
       </c>
@@ -820,8 +850,11 @@
       <c r="F6" s="2" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G6" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" s="2">
         <v>1</v>
       </c>
@@ -840,8 +873,12 @@
       <c r="F7" s="2" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G7" s="7">
+        <v>1</v>
+      </c>
+      <c r="I7" s="6"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8" s="2">
         <v>1</v>
       </c>
@@ -860,8 +897,12 @@
       <c r="F8" s="2" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G8" s="7">
+        <v>5</v>
+      </c>
+      <c r="I8" s="6"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A9" s="2">
         <v>1</v>
       </c>
@@ -880,8 +921,12 @@
       <c r="F9" s="2" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G9" s="7">
+        <v>1</v>
+      </c>
+      <c r="I9" s="6"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A10" s="3">
         <v>2</v>
       </c>
@@ -900,8 +945,12 @@
       <c r="F10" s="3" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G10" s="7">
+        <v>2</v>
+      </c>
+      <c r="I10" s="6"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A11" s="3">
         <v>2</v>
       </c>
@@ -920,8 +969,11 @@
       <c r="F11" s="3" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G11" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A12" s="3">
         <v>2</v>
       </c>
@@ -940,8 +992,11 @@
       <c r="F12" s="3" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G12" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A13" s="3">
         <v>2</v>
       </c>
@@ -960,8 +1015,11 @@
       <c r="F13" s="3" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G13" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A14" s="3">
         <v>2</v>
       </c>
@@ -980,8 +1038,11 @@
       <c r="F14" s="3" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G14" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A15" s="3">
         <v>2</v>
       </c>
@@ -1000,8 +1061,11 @@
       <c r="F15" s="3" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G15" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A16" s="3">
         <v>2</v>
       </c>
@@ -1020,8 +1084,11 @@
       <c r="F16" s="3" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G16" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17" s="4">
         <v>3</v>
       </c>
@@ -1040,8 +1107,11 @@
       <c r="F17" s="4" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G17" s="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" s="4">
         <v>3</v>
       </c>
@@ -1060,8 +1130,11 @@
       <c r="F18" s="4" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G18" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" s="4">
         <v>3</v>
       </c>
@@ -1080,8 +1153,11 @@
       <c r="F19" s="4" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G19" s="7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20" s="4">
         <v>3</v>
       </c>
@@ -1100,8 +1176,11 @@
       <c r="F20" s="4" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G20" s="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21" s="4">
         <v>3</v>
       </c>
@@ -1120,8 +1199,11 @@
       <c r="F21" s="4" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G21" s="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" s="4">
         <v>3</v>
       </c>
@@ -1140,8 +1222,11 @@
       <c r="F22" s="4" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G22" s="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23" s="5">
         <v>4</v>
       </c>
@@ -1160,8 +1245,11 @@
       <c r="F23" s="5" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G23" s="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24" s="5">
         <v>4</v>
       </c>
@@ -1180,8 +1268,11 @@
       <c r="F24" s="5" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G24" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A25" s="5">
         <v>4</v>
       </c>
@@ -1200,8 +1291,11 @@
       <c r="F25" s="5" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G25" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A26" s="5">
         <v>4</v>
       </c>
@@ -1220,8 +1314,11 @@
       <c r="F26" s="5" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G26" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A27" s="5">
         <v>4</v>
       </c>
@@ -1239,6 +1336,9 @@
       </c>
       <c r="F27" s="5" t="s">
         <v>60</v>
+      </c>
+      <c r="G27" s="7">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
